--- a/Results/Exam_Output_7.xlsx
+++ b/Results/Exam_Output_7.xlsx
@@ -1,14 +1,32 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="University Timetable" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -19,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -27,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -390,4 +417,227 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Slot 1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Slot 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BB 301
+CH 102
+CS 403
+HS 433
+ME 207
+ME 305
+ME 621
+ME 630</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CE 202
+EE 205
+EE 634
+HS 409
+HS 425
+PH 304</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CE 201
+CE 601
+CS 303
+CS 607
+EE 321
+ME 446
+ME 607</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BB 103
+EE 221
+EE 227
+EE 601
+EE 607
+MA 209
+ME 309</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CE 602
+CL 201
+CS 609
+EE 229
+MA 321
+ME 204
+ME 643</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BB 810
+CE 203
+CS 101
+CS 205
+EE 202
+EE 629
+ME 608</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CH 204
+CL 204
+CS 621
+EE 610
+MA 203
+ME 222
+PH 201
+PH 302</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CS 213
+EE 621
+EE 631
+HS 103
+MA 201
+ME 212
+ME 421
+ME 605</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CH 202
+CS 203
+EE 420
+ME 203
+ME 311
+ME 609
+PH 101
+PH 425</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CS 601
+EE 210
+EE 688
+EE 691</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CS 301
+EE 689
+EE 690
+HS 106
+HS 201</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CL 802
+CS 810
+ME 220
+ME 903</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HS 501
+MA 101
+PH 103
+PH 402</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EE 325
+EE 622
+ME 201
+ME 324</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>